--- a/inasistencias-5b-TD/alumnos-5b-TD.xlsx
+++ b/inasistencias-5b-TD/alumnos-5b-TD.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="85">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -232,6 +232,9 @@
     <t xml:space="preserve">1-codigo</t>
   </si>
   <si>
+    <t xml:space="preserve">Recup</t>
+  </si>
+  <si>
     <t xml:space="preserve">11-gray aiken</t>
   </si>
   <si>
@@ -248,6 +251,15 @@
   </si>
   <si>
     <t xml:space="preserve">valoracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arduino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presupuesto</t>
   </si>
   <si>
     <t xml:space="preserve">Recursante</t>
@@ -632,7 +644,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:XDH21"/>
   <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -641,7 +653,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="5" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="15.86"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="25" min="10" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="10" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16336" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -763,28 +775,28 @@
         <v>11</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46210</v>
+        <v>46197</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46215</v>
+        <v>46199</v>
       </c>
       <c r="AN2" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>46206</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
         <v>46220</v>
       </c>
-      <c r="AO2" s="3" t="n">
-        <v>46225</v>
-      </c>
-      <c r="AP2" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AQ2" s="3" t="n">
-        <v>46235</v>
-      </c>
       <c r="AR2" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="AT2" s="3" t="n">
         <v>46250</v>
@@ -1006,14 +1018,30 @@
       <c r="AK3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL3" s="1"/>
-      <c r="AM3" s="1"/>
-      <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1"/>
-      <c r="AQ3" s="1"/>
-      <c r="AR3" s="1"/>
-      <c r="AS3" s="1"/>
+      <c r="AL3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
@@ -1035,6 +1063,7 @@
       <c r="BL3" s="1"/>
       <c r="BM3" s="1"/>
       <c r="BN3" s="1"/>
+      <c r="XDH3" s="1"/>
     </row>
     <row r="4" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
@@ -1150,14 +1179,30 @@
       <c r="AK4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="6"/>
-      <c r="AP4" s="6"/>
-      <c r="AQ4" s="6"/>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="6"/>
+      <c r="AL4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS4" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="AT4" s="6"/>
       <c r="AU4" s="6"/>
       <c r="AV4" s="6"/>
@@ -1179,6 +1224,7 @@
       <c r="BL4" s="6"/>
       <c r="BM4" s="6"/>
       <c r="BN4" s="6"/>
+      <c r="XDH4" s="1"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1286,6 +1332,30 @@
       <c r="AK5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1393,6 +1463,30 @@
       <c r="AK6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS6" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1503,6 +1597,30 @@
       <c r="AK7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS7" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1616,14 +1734,30 @@
       <c r="AK8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="1"/>
-      <c r="AR8" s="1"/>
-      <c r="AS8" s="1"/>
+      <c r="AL8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS8" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
       <c r="AV8" s="1"/>
@@ -1645,6 +1779,7 @@
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
       <c r="BN8" s="1"/>
+      <c r="XDH8" s="1"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1756,14 +1891,30 @@
       <c r="AK9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="1"/>
-      <c r="AR9" s="1"/>
-      <c r="AS9" s="1"/>
+      <c r="AL9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS9" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT9" s="1"/>
       <c r="AU9" s="1"/>
       <c r="AV9" s="1"/>
@@ -1785,6 +1936,7 @@
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
       <c r="BN9" s="1"/>
+      <c r="XDH9" s="1"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1896,14 +2048,30 @@
       <c r="AK10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="1"/>
-      <c r="AR10" s="1"/>
-      <c r="AS10" s="1"/>
+      <c r="AL10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS10" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT10" s="1"/>
       <c r="AU10" s="1"/>
       <c r="AV10" s="1"/>
@@ -1925,6 +2093,7 @@
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
       <c r="BN10" s="1"/>
+      <c r="XDH10" s="1"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -2035,6 +2204,30 @@
       <c r="AK11" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="AL11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS11" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -2142,6 +2335,30 @@
       <c r="AK12" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS12" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -2252,6 +2469,30 @@
       <c r="AK13" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS13" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2363,14 +2604,30 @@
       <c r="AK14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="1"/>
-      <c r="AO14" s="1"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="1"/>
-      <c r="AR14" s="1"/>
-      <c r="AS14" s="1"/>
+      <c r="AL14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT14" s="1"/>
       <c r="AU14" s="1"/>
       <c r="AV14" s="1"/>
@@ -2392,6 +2649,7 @@
       <c r="BL14" s="1"/>
       <c r="BM14" s="1"/>
       <c r="BN14" s="1"/>
+      <c r="XDH14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -2503,14 +2761,30 @@
       <c r="AK15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1"/>
-      <c r="AS15" s="1"/>
+      <c r="AL15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS15" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT15" s="1"/>
       <c r="AU15" s="1"/>
       <c r="AV15" s="1"/>
@@ -2532,6 +2806,7 @@
       <c r="BL15" s="1"/>
       <c r="BM15" s="1"/>
       <c r="BN15" s="1"/>
+      <c r="XDH15" s="1"/>
     </row>
     <row r="16" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
@@ -2647,14 +2922,30 @@
       <c r="AK16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL16" s="6"/>
-      <c r="AM16" s="6"/>
-      <c r="AN16" s="6"/>
-      <c r="AO16" s="6"/>
-      <c r="AP16" s="6"/>
-      <c r="AQ16" s="6"/>
-      <c r="AR16" s="6"/>
-      <c r="AS16" s="6"/>
+      <c r="AL16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS16" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="AT16" s="6"/>
       <c r="AU16" s="6"/>
       <c r="AV16" s="6"/>
@@ -2676,6 +2967,7 @@
       <c r="BL16" s="6"/>
       <c r="BM16" s="6"/>
       <c r="BN16" s="6"/>
+      <c r="XDH16" s="1"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2786,6 +3078,30 @@
       <c r="AK17" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AL17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS17" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
@@ -2866,12 +3182,6 @@
         <f aca="false">COUNTIF(Z3:Z17,"P")</f>
         <v>9</v>
       </c>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
       <c r="AG18" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG17,"P")</f>
         <v>10</v>
@@ -2892,6 +3202,38 @@
         <f aca="false">COUNTIF(AK3:AK17,"P")</f>
         <v>12</v>
       </c>
+      <c r="AL18" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL17,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM17,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN17,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO17,"P")</f>
+        <v>10</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP17,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ17,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AR18" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR17,"P")</f>
+        <v>10</v>
+      </c>
+      <c r="AS18" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS17,"P")</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
@@ -2972,12 +3314,6 @@
         <f aca="false">COUNTIF(Z3:Z17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
       <c r="AG19" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG17,"M")</f>
         <v>0</v>
@@ -2996,6 +3332,38 @@
       </c>
       <c r="AK19" s="1" t="n">
         <f aca="false">COUNTIF(AK3:AK17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="1" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS17,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -3078,12 +3446,6 @@
         <f aca="false">COUNTIF(Z3:Z17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
       <c r="AG20" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG17,"T")</f>
         <v>0</v>
@@ -3102,6 +3464,38 @@
       </c>
       <c r="AK20" s="1" t="n">
         <f aca="false">COUNTIF(AK3:AK17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="1" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AR20" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AS20" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS17,"T")</f>
         <v>0</v>
       </c>
     </row>
@@ -3181,12 +3575,6 @@
         <f aca="false">SUM(Z18:Z20)</f>
         <v>9</v>
       </c>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
       <c r="AG21" s="1" t="n">
         <f aca="false">SUM(AG18:AG20)</f>
         <v>10</v>
@@ -3205,6 +3593,38 @@
       </c>
       <c r="AK21" s="1" t="n">
         <f aca="false">SUM(AK18:AK20)</f>
+        <v>12</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <f aca="false">SUM(AL18:AL20)</f>
+        <v>13</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <f aca="false">SUM(AM18:AM20)</f>
+        <v>13</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <f aca="false">SUM(AN18:AN20)</f>
+        <v>11</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <f aca="false">SUM(AO18:AO20)</f>
+        <v>10</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <f aca="false">SUM(AP18:AP20)</f>
+        <v>11</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <f aca="false">SUM(AQ18:AQ20)</f>
+        <v>13</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <f aca="false">SUM(AR18:AR20)</f>
+        <v>10</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <f aca="false">SUM(AS18:AS20)</f>
         <v>12</v>
       </c>
     </row>
@@ -3241,8 +3661,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16337" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3271,10 +3691,25 @@
         <v>72</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>73</v>
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3285,30 +3720,39 @@
         <v>13</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C2,D2,E2,F2,G2,H2),0)</f>
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <f aca="false">IF(I2&gt;6,"TEA",IF(I2&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+        <v>8.5</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C2,E2,F2,G2,H2,I2),0)</f>
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <f aca="false">IF(J2&gt;6,"TEA",IF(J2&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3321,31 +3765,32 @@
       <c r="C3" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" s="6" t="n">
-        <f aca="false">ROUND(AVERAGE(C3,D3,E3,F3,G3,H3),0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <f aca="false">IF(I3&gt;6,"TEA",IF(I3&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(C3,E3,F3,G3,H3,I3),0)</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="6" t="str">
+        <f aca="false">IF(J3&gt;6,"TEA",IF(J3&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>74</v>
+      <c r="L3" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3358,28 +3803,35 @@
       <c r="C4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>8.5</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C4,D4,E4,F4,G4,H4),0)</f>
-        <v>9</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f aca="false">IF(I4&gt;6,"TEA",IF(I4&gt;3,"TEP","TED"))</f>
+      <c r="J4" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C4,E4,F4,G4,H4,I4),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f aca="false">IF(J4&gt;6,"TEA",IF(J4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3390,30 +3842,39 @@
         <v>27</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C5,D5,E5,F5,G5,H5),0)</f>
-        <v>6</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <f aca="false">IF(I5&gt;6,"TEA",IF(I5&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C5,E5,F5,G5,H5,I5),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <f aca="false">IF(J5&gt;6,"TEA",IF(J5&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3426,28 +3887,35 @@
       <c r="C6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="H6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C6,D6,E6,F6,G6,H6),0)</f>
+      <c r="J6" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C6,E6,F6,G6,H6,I6),0)</f>
         <v>8</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <f aca="false">IF(I6&gt;6,"TEA",IF(I6&gt;3,"TEP","TED"))</f>
+      <c r="K6" s="1" t="str">
+        <f aca="false">IF(J6&gt;6,"TEA",IF(J6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3460,28 +3928,35 @@
       <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>9</v>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>9.25</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C7,D7,E7,F7,G7,H7),0)</f>
+      <c r="J7" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C7,E7,F7,G7,H7,I7),0)</f>
         <v>6</v>
       </c>
-      <c r="J7" s="1" t="str">
-        <f aca="false">IF(I7&gt;6,"TEA",IF(I7&gt;3,"TEP","TED"))</f>
+      <c r="K7" s="1" t="str">
+        <f aca="false">IF(J7&gt;6,"TEA",IF(J7&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3494,28 +3969,35 @@
       <c r="C8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>8.75</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C8,D8,E8,F8,G8,H8),0)</f>
+      <c r="J8" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C8,E8,F8,G8,H8,I8),0)</f>
         <v>7</v>
       </c>
-      <c r="J8" s="1" t="str">
-        <f aca="false">IF(I8&gt;6,"TEA",IF(I8&gt;3,"TEP","TED"))</f>
+      <c r="K8" s="1" t="str">
+        <f aca="false">IF(J8&gt;6,"TEA",IF(J8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3526,30 +4008,37 @@
         <v>40</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C9,D9,E9,F9,G9,H9),0)</f>
-        <v>3</v>
-      </c>
-      <c r="J9" s="1" t="str">
-        <f aca="false">IF(I9&gt;6,"TEA",IF(I9&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+      <c r="J9" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C9,E9,F9,G9,H9,I9),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K9" s="1" t="str">
+        <f aca="false">IF(J9&gt;6,"TEA",IF(J9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3562,28 +4051,35 @@
       <c r="C10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>9</v>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>8.75</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C10,D10,E10,F10,G10,H10),0)</f>
+      <c r="J10" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C10,E10,F10,G10,H10,I10),0)</f>
         <v>8</v>
       </c>
-      <c r="J10" s="1" t="str">
-        <f aca="false">IF(I10&gt;6,"TEA",IF(I10&gt;3,"TEP","TED"))</f>
+      <c r="K10" s="1" t="str">
+        <f aca="false">IF(J10&gt;6,"TEA",IF(J10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3596,28 +4092,35 @@
       <c r="C11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>8.5</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C11,D11,E11,F11,G11,H11),0)</f>
+      <c r="J11" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C11,E11,F11,G11,H11,I11),0)</f>
         <v>8</v>
       </c>
-      <c r="J11" s="1" t="str">
-        <f aca="false">IF(I11&gt;6,"TEA",IF(I11&gt;3,"TEP","TED"))</f>
+      <c r="K11" s="1" t="str">
+        <f aca="false">IF(J11&gt;6,"TEA",IF(J11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3628,30 +4131,39 @@
         <v>49</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C12,D12,E12,F12,G12,H12),0)</f>
-        <v>5</v>
-      </c>
-      <c r="J12" s="1" t="str">
-        <f aca="false">IF(I12&gt;6,"TEA",IF(I12&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>9.25</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C12,E12,F12,G12,H12,I12),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f aca="false">IF(J12&gt;6,"TEA",IF(J12&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3664,28 +4176,35 @@
       <c r="C13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>9</v>
+      <c r="F13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I13" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C13,D13,E13,F13,G13,H13),0)</f>
+        <v>9</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C13,E13,F13,G13,H13,I13),0)</f>
         <v>7</v>
       </c>
-      <c r="J13" s="1" t="str">
-        <f aca="false">IF(I13&gt;6,"TEA",IF(I13&gt;3,"TEP","TED"))</f>
+      <c r="K13" s="1" t="str">
+        <f aca="false">IF(J13&gt;6,"TEA",IF(J13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3698,28 +4217,35 @@
       <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C14,D14,E14,F14,G14,H14),0)</f>
+      <c r="J14" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C14,E14,F14,G14,H14,I14),0)</f>
         <v>4</v>
       </c>
-      <c r="J14" s="1" t="str">
-        <f aca="false">IF(I14&gt;6,"TEA",IF(I14&gt;3,"TEP","TED"))</f>
+      <c r="K14" s="1" t="str">
+        <f aca="false">IF(J14&gt;6,"TEA",IF(J14&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3732,31 +4258,32 @@
       <c r="C15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" s="6" t="n">
-        <f aca="false">ROUND(AVERAGE(C15,D15,E15,F15,G15,H15),0)</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="6" t="str">
-        <f aca="false">IF(I15&gt;6,"TEA",IF(I15&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(C15,E15,F15,G15,H15,I15),0)</f>
+        <v>1</v>
+      </c>
+      <c r="K15" s="6" t="str">
+        <f aca="false">IF(J15&gt;6,"TEA",IF(J15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>74</v>
+      <c r="L15" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3769,32 +4296,36 @@
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>9</v>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
+      <c r="H16" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="I16" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C16,D16,E16,F16,G16,H16),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C16,E16,F16,G16,H16,I16),0)</f>
         <v>8</v>
       </c>
-      <c r="J16" s="1" t="str">
-        <f aca="false">IF(I16&gt;6,"TEA",IF(I16&gt;3,"TEP","TED"))</f>
+      <c r="K16" s="1" t="str">
+        <f aca="false">IF(J16&gt;6,"TEA",IF(J16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDF16" s="1"/>
-      <c r="XDG16" s="1"/>
-      <c r="XDH16" s="1"/>
+      <c r="M16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="XDI16" s="1"/>
       <c r="XDJ16" s="1"/>
       <c r="XDK16" s="1"/>
@@ -3847,7 +4378,7 @@
     <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C2:D16">
+  <conditionalFormatting sqref="C2:E16">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -3859,7 +4390,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:J16">
+  <conditionalFormatting sqref="F2:K16">
     <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -3913,16 +4444,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4221,16 +4752,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4559,16 +5090,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4890,16 +5421,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5213,7 +5744,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inasistencias-5b-TD/alumnos-5b-TD.xlsx
+++ b/inasistencias-5b-TD/alumnos-5b-TD.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="85">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -799,7 +799,7 @@
         <v>46246</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46255</v>
@@ -1042,8 +1042,12 @@
       <c r="AS3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AT3" s="1"/>
-      <c r="AU3" s="1"/>
+      <c r="AT3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
       <c r="AX3" s="1"/>
@@ -1203,8 +1207,12 @@
       <c r="AS4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AT4" s="6"/>
-      <c r="AU4" s="6"/>
+      <c r="AT4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU4" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="AV4" s="6"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
@@ -1356,6 +1364,12 @@
       <c r="AS5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1487,6 +1501,12 @@
       <c r="AS6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU6" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1621,6 +1641,12 @@
       <c r="AS7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1758,8 +1784,12 @@
       <c r="AS8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
+      <c r="AT8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
@@ -1915,8 +1945,12 @@
       <c r="AS9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
+      <c r="AT9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
@@ -2072,8 +2106,12 @@
       <c r="AS10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT10" s="1"/>
-      <c r="AU10" s="1"/>
+      <c r="AT10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU10" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
@@ -2228,6 +2266,12 @@
       <c r="AS11" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -2359,6 +2403,12 @@
       <c r="AS12" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -2493,6 +2543,12 @@
       <c r="AS13" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2628,8 +2684,12 @@
       <c r="AS14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT14" s="1"/>
-      <c r="AU14" s="1"/>
+      <c r="AT14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
       <c r="AX14" s="1"/>
@@ -2785,8 +2845,12 @@
       <c r="AS15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
+      <c r="AT15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU15" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
@@ -2946,8 +3010,12 @@
       <c r="AS16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AT16" s="6"/>
-      <c r="AU16" s="6"/>
+      <c r="AT16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU16" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="AV16" s="6"/>
       <c r="AW16" s="6"/>
       <c r="AX16" s="6"/>
@@ -3102,6 +3170,12 @@
       <c r="AS17" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AT17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU17" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
@@ -3234,6 +3308,14 @@
         <f aca="false">COUNTIF(AS3:AS17,"P")</f>
         <v>12</v>
       </c>
+      <c r="AT18" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT17,"P")</f>
+        <v>6</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU17,"P")</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
@@ -3366,6 +3448,14 @@
         <f aca="false">COUNTIF(AS3:AS17,"M")</f>
         <v>0</v>
       </c>
+      <c r="AT19" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU17,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
@@ -3498,6 +3588,14 @@
         <f aca="false">COUNTIF(AS3:AS17,"T")</f>
         <v>0</v>
       </c>
+      <c r="AT20" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AU20" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU17,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
@@ -3626,6 +3724,14 @@
       <c r="AS21" s="1" t="n">
         <f aca="false">SUM(AS18:AS20)</f>
         <v>12</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <f aca="false">SUM(AT18:AT20)</f>
+        <v>6</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <f aca="false">SUM(AU18:AU20)</f>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-5b-TD/alumnos-5b-TD.xlsx
+++ b/inasistencias-5b-TD/alumnos-5b-TD.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="89">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">19/</t>
   </si>
   <si>
+    <t xml:space="preserve">23/)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ivan</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t xml:space="preserve">robotica</t>
   </si>
   <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thiago Benjamín</t>
   </si>
   <si>
@@ -256,10 +262,16 @@
     <t xml:space="preserve">Grupo </t>
   </si>
   <si>
-    <t xml:space="preserve">Arduino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presupuesto</t>
+    <t xml:space="preserve">materiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robot andando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 25/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 2/9</t>
   </si>
   <si>
     <t xml:space="preserve">Recursante</t>
@@ -365,7 +377,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -399,6 +411,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -644,7 +660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XDH21"/>
+  <dimension ref="A1:XDI21"/>
   <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -653,8 +669,8 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="5" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="15.86"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="10" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16336" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="45" min="10" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16337" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -805,102 +821,105 @@
         <v>46255</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="AZ2" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="BA2" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="BB2" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="BC2" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="BC2" s="3" t="n">
+      <c r="BD2" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="BD2" s="3" t="n">
-        <v>46300</v>
-      </c>
       <c r="BE2" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="BF2" s="3" t="n">
         <v>46305</v>
       </c>
-      <c r="BF2" s="3" t="n">
+      <c r="BG2" s="3" t="n">
         <v>46310</v>
       </c>
-      <c r="BG2" s="3" t="n">
+      <c r="BH2" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="BH2" s="3" t="n">
+      <c r="BI2" s="3" t="n">
         <v>46320</v>
       </c>
-      <c r="BI2" s="3" t="n">
+      <c r="BJ2" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="BJ2" s="3" t="n">
+      <c r="BK2" s="3" t="n">
         <v>46330</v>
       </c>
-      <c r="BK2" s="3" t="n">
+      <c r="BL2" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="BL2" s="3" t="n">
+      <c r="BM2" s="3" t="n">
         <v>46340</v>
       </c>
-      <c r="BM2" s="3" t="n">
+      <c r="BN2" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="BN2" s="3" t="n">
+      <c r="BO2" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="BO2" s="3" t="n">
+      <c r="BP2" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="BP2" s="3" t="n">
+      <c r="BQ2" s="3" t="n">
         <v>46360</v>
       </c>
-      <c r="BQ2" s="3" t="n">
+      <c r="BR2" s="3" t="n">
         <v>46365</v>
       </c>
-      <c r="BR2" s="3" t="n">
+      <c r="BS2" s="3" t="n">
         <v>46370</v>
       </c>
-      <c r="BS2" s="3" t="n">
+      <c r="BT2" s="3" t="n">
         <v>46375</v>
       </c>
-      <c r="BT2" s="3" t="n">
+      <c r="BU2" s="3" t="n">
         <v>46380</v>
       </c>
-      <c r="BU2" s="3" t="n">
+      <c r="BV2" s="3" t="n">
         <v>46385</v>
       </c>
-      <c r="BV2" s="3" t="n">
+      <c r="BW2" s="3" t="n">
         <v>46390</v>
       </c>
-      <c r="BW2" s="3" t="n">
+      <c r="BX2" s="3" t="n">
         <v>46395</v>
       </c>
-      <c r="BX2" s="3" t="n">
+      <c r="BY2" s="3" t="n">
         <v>46400</v>
       </c>
-      <c r="BY2" s="3" t="n">
+      <c r="BZ2" s="3" t="n">
         <v>46405</v>
       </c>
-      <c r="BZ2" s="3" t="n">
+      <c r="CA2" s="3" t="n">
         <v>46410</v>
       </c>
-      <c r="CA2" s="3" t="n">
+      <c r="CB2" s="3" t="n">
         <v>46415</v>
       </c>
-      <c r="CB2" s="3" t="n">
+      <c r="CC2" s="3" t="n">
         <v>46420</v>
       </c>
     </row>
@@ -909,75 +928,75 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R3" s="4" t="n">
         <v>0.538194444444444</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="1" t="n">
         <f aca="false">COUNTIF(E3:Z3,"P")</f>
@@ -1004,60 +1023,80 @@
         <v>8</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AV3" s="1"/>
-      <c r="AW3" s="1"/>
-      <c r="AX3" s="1"/>
-      <c r="AY3" s="1"/>
-      <c r="AZ3" s="1"/>
-      <c r="BA3" s="1"/>
-      <c r="BB3" s="1"/>
-      <c r="BC3" s="1"/>
-      <c r="BD3" s="1"/>
-      <c r="BE3" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ3" s="4" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF3" s="1"/>
       <c r="BG3" s="1"/>
       <c r="BH3" s="1"/>
@@ -1067,82 +1106,83 @@
       <c r="BL3" s="1"/>
       <c r="BM3" s="1"/>
       <c r="BN3" s="1"/>
-      <c r="XDH3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="XDI3" s="1"/>
     </row>
     <row r="4" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA4" s="6" t="n">
         <f aca="false">COUNTIF(E4:Z4,"P")</f>
@@ -1169,60 +1209,78 @@
         <v>3</v>
       </c>
       <c r="AG4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV4" s="6"/>
-      <c r="AW4" s="6"/>
-      <c r="AX4" s="6"/>
-      <c r="AY4" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="AV4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY4" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="AZ4" s="6"/>
-      <c r="BA4" s="6"/>
-      <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
-      <c r="BD4" s="6"/>
-      <c r="BE4" s="6"/>
+      <c r="BA4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BD4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE4" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="BF4" s="6"/>
       <c r="BG4" s="6"/>
       <c r="BH4" s="6"/>
@@ -1232,74 +1290,75 @@
       <c r="BL4" s="6"/>
       <c r="BM4" s="6"/>
       <c r="BN4" s="6"/>
-      <c r="XDH4" s="1"/>
+      <c r="BO4" s="6"/>
+      <c r="XDI4" s="1"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA5" s="1" t="n">
         <f aca="false">COUNTIF(E5:Z5,"P")</f>
@@ -1326,49 +1385,76 @@
         <v>9</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1376,67 +1462,67 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6" s="1" t="n">
         <f aca="false">COUNTIF(E6:Z6,"P")</f>
@@ -1463,49 +1549,76 @@
         <v>8</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1513,70 +1626,70 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA7" s="1" t="n">
         <f aca="false">COUNTIF(E7:Z7,"P")</f>
@@ -1603,49 +1716,76 @@
         <v>9</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE7" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1653,73 +1793,73 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="1" t="n">
         <f aca="false">COUNTIF(E8:Z8,"P")</f>
@@ -1746,60 +1886,78 @@
         <v>8</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AV8" s="1"/>
-      <c r="AW8" s="1"/>
-      <c r="AX8" s="1"/>
-      <c r="AY8" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="AV8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-      <c r="BB8" s="1"/>
-      <c r="BC8" s="1"/>
-      <c r="BD8" s="1"/>
-      <c r="BE8" s="1"/>
+      <c r="BA8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF8" s="1"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
@@ -1809,78 +1967,79 @@
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
       <c r="BN8" s="1"/>
-      <c r="XDH8" s="1"/>
+      <c r="BO8" s="1"/>
+      <c r="XDI8" s="1"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" s="1" t="n">
         <f aca="false">COUNTIF(E9:Z9,"P")</f>
@@ -1907,60 +2066,78 @@
         <v>8</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV9" s="1"/>
-      <c r="AW9" s="1"/>
-      <c r="AX9" s="1"/>
-      <c r="AY9" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AV9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
-      <c r="BC9" s="1"/>
-      <c r="BD9" s="1"/>
-      <c r="BE9" s="1"/>
+      <c r="BA9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF9" s="1"/>
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
@@ -1970,78 +2147,79 @@
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
       <c r="BN9" s="1"/>
-      <c r="XDH9" s="1"/>
+      <c r="BO9" s="1"/>
+      <c r="XDI9" s="1"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA10" s="1" t="n">
         <f aca="false">COUNTIF(E10:Z10,"P")</f>
@@ -2068,60 +2246,78 @@
         <v>9</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AV10" s="1"/>
-      <c r="AW10" s="1"/>
-      <c r="AX10" s="1"/>
-      <c r="AY10" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="AV10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY10" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-      <c r="BB10" s="1"/>
-      <c r="BC10" s="1"/>
-      <c r="BD10" s="1"/>
-      <c r="BE10" s="1"/>
+      <c r="BA10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE10" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF10" s="1"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
@@ -2131,77 +2327,78 @@
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
       <c r="BN10" s="1"/>
-      <c r="XDH10" s="1"/>
+      <c r="BO10" s="1"/>
+      <c r="XDI10" s="1"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA11" s="1" t="n">
         <f aca="false">COUNTIF(E11:Z11,"P")</f>
@@ -2228,49 +2425,76 @@
         <v>10</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BD11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE11" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2278,67 +2502,67 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA12" s="1" t="n">
         <f aca="false">COUNTIF(E12:Z12,"P")</f>
@@ -2365,49 +2589,76 @@
         <v>10</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE12" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2415,70 +2666,70 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA13" s="1" t="n">
         <f aca="false">COUNTIF(E13:Z13,"P")</f>
@@ -2505,49 +2756,76 @@
         <v>8</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="AV13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE13" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2555,71 +2833,71 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA14" s="1" t="n">
         <f aca="false">COUNTIF(E14:Z14,"P")</f>
@@ -2646,60 +2924,78 @@
         <v>9</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-      <c r="AX14" s="1"/>
-      <c r="AY14" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="AV14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY14" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-      <c r="BB14" s="1"/>
-      <c r="BC14" s="1"/>
-      <c r="BD14" s="1"/>
-      <c r="BE14" s="1"/>
+      <c r="BA14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE14" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF14" s="1"/>
       <c r="BG14" s="1"/>
       <c r="BH14" s="1"/>
@@ -2709,78 +3005,79 @@
       <c r="BL14" s="1"/>
       <c r="BM14" s="1"/>
       <c r="BN14" s="1"/>
-      <c r="XDH14" s="1"/>
+      <c r="BO14" s="1"/>
+      <c r="XDI14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U15" s="1"/>
       <c r="V15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA15" s="1" t="n">
         <f aca="false">COUNTIF(E15:Z15,"P")</f>
@@ -2807,60 +3104,78 @@
         <v>10</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1"/>
-      <c r="AY15" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="AV15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY15" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-      <c r="BB15" s="1"/>
-      <c r="BC15" s="1"/>
-      <c r="BD15" s="1"/>
-      <c r="BE15" s="1"/>
+      <c r="BA15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE15" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BF15" s="1"/>
       <c r="BG15" s="1"/>
       <c r="BH15" s="1"/>
@@ -2870,82 +3185,83 @@
       <c r="BL15" s="1"/>
       <c r="BM15" s="1"/>
       <c r="BN15" s="1"/>
-      <c r="XDH15" s="1"/>
+      <c r="BO15" s="1"/>
+      <c r="XDI15" s="1"/>
     </row>
     <row r="16" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA16" s="6" t="n">
         <f aca="false">COUNTIF(E16:Z16,"P")</f>
@@ -2972,60 +3288,78 @@
         <v>2</v>
       </c>
       <c r="AG16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV16" s="6"/>
-      <c r="AW16" s="6"/>
-      <c r="AX16" s="6"/>
-      <c r="AY16" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="AV16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY16" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="AZ16" s="6"/>
-      <c r="BA16" s="6"/>
-      <c r="BB16" s="6"/>
-      <c r="BC16" s="6"/>
-      <c r="BD16" s="6"/>
-      <c r="BE16" s="6"/>
+      <c r="BA16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BD16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE16" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="BF16" s="6"/>
       <c r="BG16" s="6"/>
       <c r="BH16" s="6"/>
@@ -3035,77 +3369,78 @@
       <c r="BL16" s="6"/>
       <c r="BM16" s="6"/>
       <c r="BN16" s="6"/>
-      <c r="XDH16" s="1"/>
+      <c r="BO16" s="6"/>
+      <c r="XDI16" s="1"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA17" s="1" t="n">
         <f aca="false">COUNTIF(E17:Z17,"P")</f>
@@ -3132,54 +3467,81 @@
         <v>9</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>5</v>
@@ -3316,13 +3678,50 @@
         <f aca="false">COUNTIF(AU3:AU17,"P")</f>
         <v>11</v>
       </c>
+      <c r="AV18" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV17,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW17,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="AX18" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX17,"P")</f>
+        <v>10</v>
+      </c>
+      <c r="AY18" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY17,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="AZ18" s="1"/>
+      <c r="BA18" s="1" t="n">
+        <f aca="false">COUNTIF(BA3:BA17,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="BB18" s="1" t="n">
+        <f aca="false">COUNTIF(BB3:BB17,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="BC18" s="1" t="n">
+        <f aca="false">COUNTIF(BC3:BC17,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="BD18" s="1" t="n">
+        <f aca="false">COUNTIF(BD3:BD17,"P")</f>
+        <v>10</v>
+      </c>
+      <c r="BE18" s="1" t="n">
+        <f aca="false">COUNTIF(BE3:BE17,"P")</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"M")</f>
@@ -3454,6 +3853,43 @@
       </c>
       <c r="AU19" s="1" t="n">
         <f aca="false">COUNTIF(AU3:AU17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY17,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="1"/>
+      <c r="BA19" s="1" t="n">
+        <f aca="false">COUNTIF(BA3:BA17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="1" t="n">
+        <f aca="false">COUNTIF(BB3:BB17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="BC19" s="1" t="n">
+        <f aca="false">COUNTIF(BC3:BC17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="1" t="n">
+        <f aca="false">COUNTIF(BD3:BD17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="1" t="n">
+        <f aca="false">COUNTIF(BE3:BE17,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -3462,7 +3898,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"T")</f>
@@ -3594,6 +4030,43 @@
       </c>
       <c r="AU20" s="1" t="n">
         <f aca="false">COUNTIF(AU3:AU17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="1"/>
+      <c r="BA20" s="1" t="n">
+        <f aca="false">COUNTIF(BA3:BA17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="1" t="n">
+        <f aca="false">COUNTIF(BB3:BB17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="BC20" s="1" t="n">
+        <f aca="false">COUNTIF(BC3:BC17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="BD20" s="1" t="n">
+        <f aca="false">COUNTIF(BD3:BD17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="1" t="n">
+        <f aca="false">COUNTIF(BE3:BE17,"T")</f>
         <v>0</v>
       </c>
     </row>
@@ -3732,6 +4205,43 @@
       <c r="AU21" s="1" t="n">
         <f aca="false">SUM(AU18:AU20)</f>
         <v>11</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <f aca="false">SUM(AV18:AV20)</f>
+        <v>13</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <f aca="false">SUM(AW18:AW20)</f>
+        <v>11</v>
+      </c>
+      <c r="AX21" s="1" t="n">
+        <f aca="false">SUM(AX18:AX20)</f>
+        <v>10</v>
+      </c>
+      <c r="AY21" s="1" t="n">
+        <f aca="false">SUM(AY18:AY20)</f>
+        <v>9</v>
+      </c>
+      <c r="AZ21" s="1"/>
+      <c r="BA21" s="1" t="n">
+        <f aca="false">SUM(BA18:BA20)</f>
+        <v>9</v>
+      </c>
+      <c r="BB21" s="1" t="n">
+        <f aca="false">SUM(BB18:BB20)</f>
+        <v>9</v>
+      </c>
+      <c r="BC21" s="1" t="n">
+        <f aca="false">SUM(BC18:BC20)</f>
+        <v>12</v>
+      </c>
+      <c r="BD21" s="1" t="n">
+        <f aca="false">SUM(BD18:BD20)</f>
+        <v>10</v>
+      </c>
+      <c r="BE21" s="1" t="n">
+        <f aca="false">SUM(BE18:BE20)</f>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3767,8 +4277,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16337" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="4" style="1" width="12.8"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="6" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16335" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3779,43 +4292,49 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3823,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>6</v>
@@ -3857,95 +4376,128 @@
       <c r="M2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="N2" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="O2" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="6" t="n">
+      <c r="A3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,F3,G3,H3,I3),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K3" s="6" t="str">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="str">
         <f aca="false">IF(J3&gt;6,"TEA",IF(J3&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>TEP</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="XDG3" s="1"/>
+      <c r="XDH3" s="1"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="J4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,F4,G4,H4,I4),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1" t="str">
         <f aca="false">IF(J4&gt;6,"TEA",IF(J4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>6</v>
@@ -3954,19 +4506,19 @@
         <v>46220</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="J5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C5,E5,F5,G5,H5,I5),0)</f>
@@ -3977,28 +4529,37 @@
         <v>TEA</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>8</v>
@@ -4007,7 +4568,7 @@
         <v>9</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="J6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C6,E6,F6,G6,H6,I6),0)</f>
@@ -4018,201 +4579,233 @@
         <v>TEA</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>9.25</v>
+        <v>8.5</v>
       </c>
       <c r="J7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,F7,G7,H7,I7),0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1" t="str">
         <f aca="false">IF(J7&gt;6,"TEA",IF(J7&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>TEA</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="G8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="J8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,F8,G8,H8,I8),0)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1" t="str">
         <f aca="false">IF(J8&gt;6,"TEA",IF(J8&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
+        <v>TEP</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="J9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C9,E9,F9,G9,H9,I9),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="str">
         <f aca="false">IF(J9&gt;6,"TEA",IF(J9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="E10" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="J10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,F10,G10,H10,I10),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" s="1" t="str">
         <f aca="false">IF(J10&gt;6,"TEA",IF(J10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,F11,G11,H11,I11),0)</f>
@@ -4223,30 +4816,34 @@
         <v>TEA</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>46220</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
@@ -4255,7 +4852,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="J12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,F12,G12,H12,I12),0)</f>
@@ -4266,10 +4863,13 @@
         <v>TEA</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4277,7 +4877,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>7</v>
@@ -4309,57 +4909,64 @@
       <c r="M13" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="N13" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="O13" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,F14,G14,H14,I14),0)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K14" s="1" t="str">
         <f aca="false">IF(J14&gt;6,"TEA",IF(J14&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>2</v>
+        <v>TEA</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>1</v>
@@ -4375,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>1</v>
@@ -4389,49 +4996,52 @@
         <v>TED</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="XDG15" s="1"/>
+      <c r="XDH15" s="1"/>
     </row>
     <row r="16" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1" t="n">
+      <c r="A16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,F16,G16,H16,I16),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K16" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" s="6" t="str">
         <f aca="false">IF(J16&gt;6,"TEA",IF(J16&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>TED</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="XDG16" s="1"/>
+      <c r="XDH16" s="1"/>
       <c r="XDI16" s="1"/>
       <c r="XDJ16" s="1"/>
       <c r="XDK16" s="1"/>
@@ -4550,16 +5160,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4567,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -4581,7 +5191,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -4595,10 +5205,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -4612,10 +5222,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -4629,10 +5239,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -4651,7 +5261,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>6</v>
@@ -4662,7 +5272,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -4676,10 +5286,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -4693,7 +5303,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -4707,10 +5317,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>4</v>
@@ -4724,10 +5334,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -4741,7 +5351,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1</v>
@@ -4755,10 +5365,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>7</v>
@@ -4772,10 +5382,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -4789,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>1</v>
@@ -4803,10 +5413,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>10</v>
@@ -4858,16 +5468,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4875,10 +5485,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -4892,7 +5502,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -4906,10 +5516,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>8</v>
@@ -4923,10 +5533,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>8</v>
@@ -4940,10 +5550,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>10</v>
@@ -4957,10 +5567,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -4974,10 +5584,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -4991,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5005,10 +5615,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>10</v>
@@ -5022,10 +5632,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>10</v>
@@ -5039,10 +5649,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -5056,10 +5666,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -5078,7 +5688,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>7</v>
@@ -5086,7 +5696,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>7</v>
@@ -5094,7 +5704,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>6</v>
@@ -5105,10 +5715,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>7</v>
@@ -5122,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -5136,10 +5746,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>10</v>
@@ -5196,16 +5806,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5213,7 +5823,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -5227,7 +5837,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -5241,10 +5851,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>9</v>
@@ -5258,10 +5868,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>9</v>
@@ -5275,10 +5885,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -5292,10 +5902,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9</v>
@@ -5309,10 +5919,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>7</v>
@@ -5326,7 +5936,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5340,10 +5950,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>10</v>
@@ -5362,7 +5972,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>8</v>
@@ -5373,10 +5983,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -5390,10 +6000,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -5407,10 +6017,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -5429,7 +6039,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>9</v>
@@ -5440,10 +6050,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>2</v>
@@ -5457,7 +6067,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -5471,10 +6081,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -5527,16 +6137,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5544,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -5558,7 +6168,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -5572,10 +6182,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -5589,10 +6199,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -5606,10 +6216,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>9</v>
@@ -5628,7 +6238,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>6</v>
@@ -5639,7 +6249,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -5653,7 +6263,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5667,7 +6277,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -5681,10 +6291,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>10</v>
@@ -5703,7 +6313,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -5711,7 +6321,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -5722,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -5736,7 +6346,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -5750,7 +6360,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>1</v>
@@ -5764,10 +6374,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>2</v>
@@ -5781,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -5795,10 +6405,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>6</v>
@@ -5850,7 +6460,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5858,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -5869,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -5880,10 +6490,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>8.5</v>
@@ -5894,7 +6504,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -5905,10 +6515,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -5919,10 +6529,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9.25</v>
@@ -5933,10 +6543,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8.75</v>
@@ -5947,10 +6557,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4.5</v>
@@ -5961,10 +6571,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>8.75</v>
@@ -5975,10 +6585,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>8.5</v>
@@ -5989,7 +6599,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -6000,10 +6610,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -6014,10 +6624,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>3</v>
@@ -6028,7 +6638,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -6039,7 +6649,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>1</v>
